--- a/Lab5/task3/Task3.xlsx
+++ b/Lab5/task3/Task3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harry\Desktop\Project\NYCU_DL\Lab5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harry\Desktop\Project\NYCU_DL\Lab5\task3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B0A398-D22E-43F4-B17E-E3FA3ECD9C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37EF9E06-4E34-4E03-83EA-042F7E7EA7D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{644334D1-339E-4C9E-868D-7F46A5EBFFB2}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="17">
   <si>
     <t>Batch Size</t>
   </si>
@@ -101,6 +101,10 @@
   </si>
   <si>
     <t>0.00025+clip</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>600K</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -193,7 +197,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -213,6 +217,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -779,7 +786,45 @@
       <c r="N5"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="M6" s="1"/>
+      <c r="A6" s="7">
+        <v>32</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="7">
+        <v>0.99</v>
+      </c>
+      <c r="D6" s="7">
+        <v>200000</v>
+      </c>
+      <c r="E6" s="7">
+        <v>200000</v>
+      </c>
+      <c r="F6" s="7">
+        <v>2000</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0.99997499999999995</v>
+      </c>
+      <c r="H6" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" s="7">
+        <v>3</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>16</v>
+      </c>
       <c r="N6"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.4">

--- a/Lab5/task3/Task3.xlsx
+++ b/Lab5/task3/Task3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harry\Desktop\Project\NYCU_DL\Lab5\task3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37EF9E06-4E34-4E03-83EA-042F7E7EA7D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{989C3A22-4430-4A3C-BB5A-E9D77062CF47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{644334D1-339E-4C9E-868D-7F46A5EBFFB2}"/>
   </bookViews>
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5D748CC-00BA-41B6-A90C-D981F2C3F76F}">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="11.54296875" style="1" customWidth="1"/>
@@ -805,10 +805,10 @@
         <v>2000</v>
       </c>
       <c r="G6" s="7">
-        <v>0.99997499999999995</v>
+        <v>0.99995999999999996</v>
       </c>
       <c r="H6" s="7">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>9</v>
@@ -850,10 +850,6 @@
     <row r="12" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M12" s="1"/>
       <c r="N12"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="M13" s="1"/>
-      <c r="N13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Lab5/task3/Task3.xlsx
+++ b/Lab5/task3/Task3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harry\Desktop\Project\NYCU_DL\Lab5\task3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{989C3A22-4430-4A3C-BB5A-E9D77062CF47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E96A5C3-5F24-4EC1-B529-312B7E907741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{644334D1-339E-4C9E-868D-7F46A5EBFFB2}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
   <si>
     <t>Batch Size</t>
   </si>
@@ -105,6 +105,14 @@
   </si>
   <si>
     <t>600K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dealing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BEST</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -145,7 +153,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -182,6 +190,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -197,7 +217,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -219,7 +239,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -825,11 +848,53 @@
       <c r="M6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="N6"/>
+      <c r="N6" s="7" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="M7" s="1"/>
-      <c r="N7"/>
+      <c r="A7" s="7">
+        <v>32</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="8">
+        <v>0.99</v>
+      </c>
+      <c r="D7" s="8">
+        <v>200000</v>
+      </c>
+      <c r="E7" s="8">
+        <v>200000</v>
+      </c>
+      <c r="F7" s="8">
+        <v>2000</v>
+      </c>
+      <c r="G7" s="8">
+        <v>0.99995999999999996</v>
+      </c>
+      <c r="H7" s="8">
+        <v>0.01</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="L7" s="8">
+        <v>3</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="M8" s="1"/>
